--- a/survey_templates/032_language_learning_styles_survey--survey_templates.xlsx
+++ b/survey_templates/032_language_learning_styles_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -711,8 +711,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -740,12 +740,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'visual'}</t>
+          <t>visual</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Visual'}</t>
+          <t>Visual</t>
         </is>
       </c>
     </row>
@@ -757,12 +757,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'auditory'}</t>
+          <t>auditory</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Auditory'}</t>
+          <t>Auditory</t>
         </is>
       </c>
     </row>
@@ -774,12 +774,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'kinesthetic'}</t>
+          <t>kinesthetic</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Kinesthetic'}</t>
+          <t>Kinesthetic</t>
         </is>
       </c>
     </row>
@@ -791,12 +791,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'tactile'}</t>
+          <t>tactile</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Tactile'}</t>
+          <t>Tactile</t>
         </is>
       </c>
     </row>
@@ -808,12 +808,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -825,12 +825,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'storytelling'}</t>
+          <t>storytelling</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Storytelling'}</t>
+          <t>Storytelling</t>
         </is>
       </c>
     </row>
@@ -842,12 +842,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'videos'}</t>
+          <t>videos</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Videos'}</t>
+          <t>Videos</t>
         </is>
       </c>
     </row>
@@ -859,12 +859,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'games'}</t>
+          <t>games</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Games'}</t>
+          <t>Games</t>
         </is>
       </c>
     </row>
@@ -876,12 +876,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'textbooks'}</t>
+          <t>textbooks</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Textbooks'}</t>
+          <t>Textbooks</t>
         </is>
       </c>
     </row>
@@ -893,12 +893,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'fast-paced'}</t>
+          <t>fast-paced</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Fast-paced'}</t>
+          <t>Fast-paced</t>
         </is>
       </c>
     </row>
@@ -910,12 +910,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'self-paced'}</t>
+          <t>self-paced</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Self-paced'}</t>
+          <t>Self-paced</t>
         </is>
       </c>
     </row>
@@ -927,12 +927,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'collaborative'}</t>
+          <t>collaborative</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Collaborative'}</t>
+          <t>Collaborative</t>
         </is>
       </c>
     </row>
@@ -944,12 +944,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'individualized'}</t>
+          <t>individualized</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Individualized'}</t>
+          <t>Individualized</t>
         </is>
       </c>
     </row>
